--- a/data/trans_dic/P33_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P33_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,57; 13,34</t>
+          <t>7,76; 13,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,74; 19,54</t>
+          <t>12,64; 19,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,86; 20,29</t>
+          <t>12,99; 20,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 16,07</t>
+          <t>4,65; 14,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,35; 15,24</t>
+          <t>9,64; 15,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,91; 27,39</t>
+          <t>18,81; 27,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,05; 23,0</t>
+          <t>14,97; 22,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,22; 21,02</t>
+          <t>11,61; 22,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,31; 13,31</t>
+          <t>9,35; 13,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,54; 22,01</t>
+          <t>16,74; 21,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,8; 20,17</t>
+          <t>15,13; 20,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,34; 16,13</t>
+          <t>9,11; 16,21</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,61; 14,86</t>
+          <t>9,7; 14,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,34; 22,66</t>
+          <t>16,61; 22,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,58; 21,16</t>
+          <t>14,67; 21,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,3; 20,62</t>
+          <t>10,89; 19,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,44; 18,46</t>
+          <t>12,73; 18,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,57; 24,22</t>
+          <t>17,52; 24,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,55; 18,43</t>
+          <t>12,7; 18,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,63; 22,91</t>
+          <t>16,16; 23,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,78; 15,79</t>
+          <t>11,86; 15,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,73; 22,3</t>
+          <t>17,98; 22,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,49; 18,92</t>
+          <t>14,52; 18,91</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,99; 20,19</t>
+          <t>14,66; 20,68</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,24; 19,21</t>
+          <t>13,47; 19,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,25; 24,78</t>
+          <t>17,97; 24,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,47; 23,03</t>
+          <t>16,51; 22,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,58; 23,79</t>
+          <t>16,59; 23,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,11; 19,9</t>
+          <t>13,92; 19,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,38; 26,08</t>
+          <t>19,6; 26,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,12; 24,4</t>
+          <t>17,94; 24,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,19; 26,16</t>
+          <t>20,49; 26,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,57; 18,88</t>
+          <t>14,61; 18,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,86; 24,29</t>
+          <t>19,83; 24,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,23; 22,61</t>
+          <t>18,07; 22,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,54; 24,2</t>
+          <t>19,26; 23,84</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>28,17%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,97; 21,22</t>
+          <t>13,8; 20,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,96; 30,48</t>
+          <t>22,59; 30,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,28; 24,17</t>
+          <t>17,64; 24,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,66; 29,8</t>
+          <t>24,23; 31,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,85; 24,86</t>
+          <t>17,5; 25,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,97; 37,3</t>
+          <t>29,24; 37,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,16; 31,27</t>
+          <t>23,77; 31,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,45; 30,06</t>
+          <t>26,07; 31,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,75; 21,96</t>
+          <t>16,6; 21,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27,13; 32,72</t>
+          <t>27,19; 32,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,56; 26,77</t>
+          <t>21,82; 26,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,68; 28,6</t>
+          <t>25,76; 30,38</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,19; 25,52</t>
+          <t>17,35; 25,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,29; 31,05</t>
+          <t>21,96; 30,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,8; 29,4</t>
+          <t>20,5; 28,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,51; 33,23</t>
+          <t>25,66; 32,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,94; 31,22</t>
+          <t>22,63; 30,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,03; 45,92</t>
+          <t>36,08; 46,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,67; 39,48</t>
+          <t>30,53; 39,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>35,83; 41,94</t>
+          <t>35,71; 41,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,05; 27,1</t>
+          <t>20,99; 26,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,88; 37,33</t>
+          <t>30,63; 37,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26,56; 32,74</t>
+          <t>26,63; 32,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,64; 36,56</t>
+          <t>31,36; 36,29</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>37,64%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30,19; 41,51</t>
+          <t>30,7; 41,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39,8; 52,07</t>
+          <t>39,71; 51,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31,33; 42,02</t>
+          <t>31,33; 42,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30,87; 38,66</t>
+          <t>31,09; 38,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38,52; 48,5</t>
+          <t>38,22; 48,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,74; 52,06</t>
+          <t>41,3; 51,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41,81; 52,54</t>
+          <t>42,0; 52,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39,4; 83,74</t>
+          <t>37,07; 43,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36,02; 43,58</t>
+          <t>35,84; 43,37</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42,22; 50,31</t>
+          <t>42,46; 50,37</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38,71; 46,01</t>
+          <t>38,41; 45,83</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36,93; 76,14</t>
+          <t>35,22; 40,23</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,49%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>35,36; 48,41</t>
+          <t>35,84; 49,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40,44; 54,08</t>
+          <t>40,67; 54,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37,24; 48,63</t>
+          <t>36,93; 48,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34,93; 44,76</t>
+          <t>34,76; 43,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>47,47; 59,34</t>
+          <t>47,56; 59,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,73; 61,83</t>
+          <t>51,16; 61,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,48; 51,58</t>
+          <t>40,03; 51,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>44,99; 52,07</t>
+          <t>44,6; 51,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>44,4; 53,41</t>
+          <t>44,81; 53,88</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48,97; 56,71</t>
+          <t>48,48; 57,17</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40,16; 48,61</t>
+          <t>40,69; 48,75</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>42,26; 47,76</t>
+          <t>41,81; 47,21</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,19; 20,02</t>
+          <t>17,16; 20,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24,38; 27,59</t>
+          <t>24,21; 27,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21,51; 24,65</t>
+          <t>21,7; 24,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,66; 25,73</t>
+          <t>22,96; 26,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,67; 25,58</t>
+          <t>22,68; 25,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,97; 34,37</t>
+          <t>30,84; 34,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,96; 30,1</t>
+          <t>26,98; 30,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>29,45; 46,78</t>
+          <t>29,43; 32,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20,39; 22,39</t>
+          <t>20,32; 22,3</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28,05; 30,32</t>
+          <t>28,27; 30,45</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24,85; 27,06</t>
+          <t>24,81; 27,04</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>25,42; 35,64</t>
+          <t>26,65; 28,7</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33352</t>
+          <t>33786</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>45925</t>
+          <t>58437</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79277</t>
+          <t>92224</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36926; 65067</t>
+          <t>37860; 66740</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57632; 88367</t>
+          <t>57177; 86403</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53958; 85107</t>
+          <t>54504; 86235</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16434; 59632</t>
+          <t>17869; 55537</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>43468; 70824</t>
+          <t>44790; 71131</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81181; 117568</t>
+          <t>80730; 116149</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59406; 90802</t>
+          <t>59111; 90521</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31265; 64326</t>
+          <t>41207; 78857</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>88640; 126712</t>
+          <t>89018; 128482</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>145838; 194000</t>
+          <t>147555; 191776</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>120512; 164210</t>
+          <t>123237; 165052</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>56513; 109269</t>
+          <t>67278; 119782</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63803</t>
+          <t>66899</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>89724</t>
+          <t>96431</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>153526</t>
+          <t>163330</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>69771; 107888</t>
+          <t>70464; 106438</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>112083; 155466</t>
+          <t>113939; 154862</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86123; 124920</t>
+          <t>86625; 124856</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45957; 83884</t>
+          <t>50125; 87992</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>77220; 114631</t>
+          <t>79057; 113563</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>107006; 147569</t>
+          <t>106756; 147612</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70477; 103534</t>
+          <t>71336; 105184</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53314; 114897</t>
+          <t>79032; 117213</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>158675; 212702</t>
+          <t>159759; 210868</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>229668; 288902</t>
+          <t>232872; 297727</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>166927; 217975</t>
+          <t>167261; 217884</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>117969; 183378</t>
+          <t>139154; 196338</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>106694</t>
+          <t>119669</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>119740</t>
+          <t>139214</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>226434</t>
+          <t>258884</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>82847; 120275</t>
+          <t>84341; 122091</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>123921; 168288</t>
+          <t>122027; 169459</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>109923; 153728</t>
+          <t>110226; 150982</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86764; 124523</t>
+          <t>100513; 141779</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>96926; 136688</t>
+          <t>95621; 136097</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>137417; 184857</t>
+          <t>138956; 186621</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>119823; 161399</t>
+          <t>118662; 158921</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>105182; 136256</t>
+          <t>122380; 157144</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>191329; 247880</t>
+          <t>191836; 244376</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>275672; 337168</t>
+          <t>275173; 337415</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>242313; 300493</t>
+          <t>240141; 299373</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>204009; 252748</t>
+          <t>231642; 286826</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>178328</t>
+          <t>190383</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>189220</t>
+          <t>206172</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>367548</t>
+          <t>396556</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71590; 108691</t>
+          <t>70694; 107079</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>140667; 186694</t>
+          <t>138403; 186341</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>111257; 155627</t>
+          <t>113536; 156337</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84351; 260208</t>
+          <t>165939; 217190</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>91512; 127416</t>
+          <t>89679; 128516</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>178527; 229863</t>
+          <t>180169; 229438</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>156064; 202007</t>
+          <t>153551; 200767</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>156964; 210174</t>
+          <t>188396; 224921</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>171631; 225062</t>
+          <t>170091; 224668</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>333403; 402009</t>
+          <t>334120; 402993</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>278128; 345301</t>
+          <t>281373; 345358</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>215080; 449670</t>
+          <t>362561; 427595</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>158129</t>
+          <t>171953</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>205557</t>
+          <t>228373</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>363686</t>
+          <t>400327</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>65532; 97290</t>
+          <t>66147; 97154</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>95185; 132596</t>
+          <t>93794; 132242</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>99147; 140145</t>
+          <t>97727; 138025</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>139258; 181450</t>
+          <t>152302; 194012</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>91955; 125135</t>
+          <t>90712; 123955</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>160594; 204701</t>
+          <t>160819; 205259</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>152059; 195743</t>
+          <t>151348; 195217</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>188999; 221246</t>
+          <t>210264; 245941</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>164646; 211928</t>
+          <t>164189; 210165</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>269542; 325803</t>
+          <t>267330; 324467</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258342; 318398</t>
+          <t>258942; 319592</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>339635; 392469</t>
+          <t>370768; 429030</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>126155</t>
+          <t>139933</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>364379</t>
+          <t>172431</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>490535</t>
+          <t>312364</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>87489; 120284</t>
+          <t>88952; 120587</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>123290; 161319</t>
+          <t>123006; 159875</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>104737; 140472</t>
+          <t>104748; 140605</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>112044; 140333</t>
+          <t>124562; 155327</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>130263; 164020</t>
+          <t>129261; 163693</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>147402; 183820</t>
+          <t>145816; 180911</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>157520; 197971</t>
+          <t>158241; 197358</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>235972; 501476</t>
+          <t>159129; 187519</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>226223; 273695</t>
+          <t>225048; 272364</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>279860; 333470</t>
+          <t>281465; 333929</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>275269; 327193</t>
+          <t>273166; 325903</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>355216; 732302</t>
+          <t>292304; 333861</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>108240</t>
+          <t>117622</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>196451</t>
+          <t>212014</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>304691</t>
+          <t>329636</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>72965; 99900</t>
+          <t>73949; 101507</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>99778; 133421</t>
+          <t>100350; 133966</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>95069; 124147</t>
+          <t>94278; 122982</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>95500; 122389</t>
+          <t>104112; 130747</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>158077; 197580</t>
+          <t>158370; 198420</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>199960; 239010</t>
+          <t>197753; 236955</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>159301; 202945</t>
+          <t>157527; 203822</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>182017; 210668</t>
+          <t>196864; 227519</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>239446; 288070</t>
+          <t>241664; 290622</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>310121; 359159</t>
+          <t>307001; 362025</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>260559; 315376</t>
+          <t>263949; 316258</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>286479; 323816</t>
+          <t>309773; 349770</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>774702</t>
+          <t>840246</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1210995</t>
+          <t>1113074</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1985697</t>
+          <t>1953320</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>555227; 646675</t>
+          <t>554047; 649763</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>832387; 941945</t>
+          <t>826532; 934936</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>728777; 834909</t>
+          <t>735103; 838273</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>592845; 863876</t>
+          <t>787282; 894029</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>760929; 858862</t>
+          <t>761366; 861081</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1099157; 1219663</t>
+          <t>1094611; 1216383</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>951601; 1062651</t>
+          <t>952532; 1062267</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1047790; 1664509</t>
+          <t>1066597; 1169690</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1342973; 1474587</t>
+          <t>1338686; 1468943</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1952772; 2111054</t>
+          <t>1968252; 2120077</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1718801; 1871601</t>
+          <t>1716459; 1870789</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1757557; 2464388</t>
+          <t>1879397; 2023902</t>
         </is>
       </c>
     </row>
